--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/113.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/113.xlsx
@@ -426,13 +426,13 @@
         <v>5.720968158359988</v>
       </c>
       <c r="E2">
-        <v>-11.84559797139375</v>
+        <v>-14.79475308346704</v>
       </c>
       <c r="F2">
-        <v>-3.640530746623248</v>
+        <v>-4.239726165601256</v>
       </c>
       <c r="G2">
-        <v>-5.631623136251179</v>
+        <v>-8.85343612343328</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>5.710405018168107</v>
       </c>
       <c r="E3">
-        <v>-11.81696895871725</v>
+        <v>-13.94877074019811</v>
       </c>
       <c r="F3">
-        <v>-3.880620612813642</v>
+        <v>-4.244770923084305</v>
       </c>
       <c r="G3">
-        <v>-5.213395297183971</v>
+        <v>-8.039270348414778</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>5.640513754498443</v>
       </c>
       <c r="E4">
-        <v>-13.21901168233604</v>
+        <v>-16.40535467750909</v>
       </c>
       <c r="F4">
-        <v>-3.975872095359349</v>
+        <v>-4.136427093737352</v>
       </c>
       <c r="G4">
-        <v>-4.780518294105488</v>
+        <v>-7.863192362817561</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.527953043999551</v>
       </c>
       <c r="E5">
-        <v>-13.69173002704874</v>
+        <v>-16.57672119090735</v>
       </c>
       <c r="F5">
-        <v>-3.560589150416082</v>
+        <v>-3.840530943987758</v>
       </c>
       <c r="G5">
-        <v>-4.92595718073675</v>
+        <v>-9.579183848188928</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.406316573548392</v>
       </c>
       <c r="E6">
-        <v>-12.78839908894667</v>
+        <v>-16.68294560570527</v>
       </c>
       <c r="F6">
-        <v>-3.825834877894692</v>
+        <v>-4.216636252615623</v>
       </c>
       <c r="G6">
-        <v>-5.316902814014824</v>
+        <v>-8.254220759734116</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.301459220389052</v>
       </c>
       <c r="E7">
-        <v>-14.06634351085926</v>
+        <v>-17.85412219593902</v>
       </c>
       <c r="F7">
-        <v>-3.696682459389415</v>
+        <v>-3.991195235576335</v>
       </c>
       <c r="G7">
-        <v>-5.042339409169829</v>
+        <v>-8.474905035927474</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>5.249735296386716</v>
       </c>
       <c r="E8">
-        <v>-15.69191623997066</v>
+        <v>-18.469292747511</v>
       </c>
       <c r="F8">
-        <v>-3.54137599687555</v>
+        <v>-3.863306077360327</v>
       </c>
       <c r="G8">
-        <v>-5.193846525774575</v>
+        <v>-8.577459115643016</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>5.28567618309229</v>
       </c>
       <c r="E9">
-        <v>-15.26843146466936</v>
+        <v>-19.18779401899</v>
       </c>
       <c r="F9">
-        <v>-3.656446169533235</v>
+        <v>-3.603994773955373</v>
       </c>
       <c r="G9">
-        <v>-4.609849739919441</v>
+        <v>-8.331432613346539</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.423748462776708</v>
       </c>
       <c r="E10">
-        <v>-16.23934082038789</v>
+        <v>-18.05895413225397</v>
       </c>
       <c r="F10">
-        <v>-3.945179426350822</v>
+        <v>-3.666604438993765</v>
       </c>
       <c r="G10">
-        <v>-4.482887007942852</v>
+        <v>-8.275918075198501</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.677797333176629</v>
       </c>
       <c r="E11">
-        <v>-16.25797096245545</v>
+        <v>-19.22296667660758</v>
       </c>
       <c r="F11">
-        <v>-3.636923206584056</v>
+        <v>-3.829014151986636</v>
       </c>
       <c r="G11">
-        <v>-3.551332598647332</v>
+        <v>-7.470200812396218</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>6.045076621113625</v>
       </c>
       <c r="E12">
-        <v>-17.03320042782854</v>
+        <v>-20.33842945112496</v>
       </c>
       <c r="F12">
-        <v>-3.298265903134548</v>
+        <v>-3.87115403013445</v>
       </c>
       <c r="G12">
-        <v>-3.166296289156858</v>
+        <v>-6.858666908745426</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>6.495129964157714</v>
       </c>
       <c r="E13">
-        <v>-17.34068834142336</v>
+        <v>-20.66737327456812</v>
       </c>
       <c r="F13">
-        <v>-3.42278609112337</v>
+        <v>-3.424329339594785</v>
       </c>
       <c r="G13">
-        <v>-3.177025767249635</v>
+        <v>-6.879877574015537</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>7.002901141945069</v>
       </c>
       <c r="E14">
-        <v>-19.00321341843736</v>
+        <v>-22.16503472685887</v>
       </c>
       <c r="F14">
-        <v>-3.430885867587943</v>
+        <v>-3.343707653749921</v>
       </c>
       <c r="G14">
-        <v>-2.995849541521941</v>
+        <v>-6.167666669969969</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>7.531454481703497</v>
       </c>
       <c r="E15">
-        <v>-20.04199101410885</v>
+        <v>-23.52641628236279</v>
       </c>
       <c r="F15">
-        <v>-3.008226310922746</v>
+        <v>-3.332017732961614</v>
       </c>
       <c r="G15">
-        <v>-2.213895374600547</v>
+        <v>-5.522673082553764</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>8.032904986049392</v>
       </c>
       <c r="E16">
-        <v>-19.73361099113451</v>
+        <v>-24.54563992726916</v>
       </c>
       <c r="F16">
-        <v>-3.059088069454636</v>
+        <v>-2.586568250447533</v>
       </c>
       <c r="G16">
-        <v>-1.422161856156147</v>
+        <v>-5.114105415370149</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>8.480896931588463</v>
       </c>
       <c r="E17">
-        <v>-21.42276349531361</v>
+        <v>-24.78918125940167</v>
       </c>
       <c r="F17">
-        <v>-2.819168846949218</v>
+        <v>-3.094170257330597</v>
       </c>
       <c r="G17">
-        <v>-1.23849941072846</v>
+        <v>-4.670922684027916</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>8.848606706552532</v>
       </c>
       <c r="E18">
-        <v>-21.94380065768814</v>
+        <v>-25.49952222071885</v>
       </c>
       <c r="F18">
-        <v>-2.8641400848798</v>
+        <v>-2.739841899354929</v>
       </c>
       <c r="G18">
-        <v>-0.4697377677810619</v>
+        <v>-4.516618156442486</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>9.111446479621371</v>
       </c>
       <c r="E19">
-        <v>-23.33034694325269</v>
+        <v>-25.40050260806713</v>
       </c>
       <c r="F19">
-        <v>-2.578975434833473</v>
+        <v>-2.898331777797752</v>
       </c>
       <c r="G19">
-        <v>-0.2891607507959758</v>
+        <v>-3.571685832622772</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>9.270466560828813</v>
       </c>
       <c r="E20">
-        <v>-23.43744535353409</v>
+        <v>-26.26614758547736</v>
       </c>
       <c r="F20">
-        <v>-2.229561780658614</v>
+        <v>-2.612900393447724</v>
       </c>
       <c r="G20">
-        <v>-0.01828860422726795</v>
+        <v>-3.300860033691614</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>9.325334768397228</v>
       </c>
       <c r="E21">
-        <v>-24.32985814080366</v>
+        <v>-27.35673998074461</v>
       </c>
       <c r="F21">
-        <v>-2.235238582469999</v>
+        <v>-2.047650642269037</v>
       </c>
       <c r="G21">
-        <v>0.3448815519763205</v>
+        <v>-3.700661376287238</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>9.278437109249444</v>
       </c>
       <c r="E22">
-        <v>-24.97414225177096</v>
+        <v>-27.28977290711919</v>
       </c>
       <c r="F22">
-        <v>-2.046398979123406</v>
+        <v>-2.215552431142468</v>
       </c>
       <c r="G22">
-        <v>0.1220851477289089</v>
+        <v>-3.449678987318471</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>9.149901257454591</v>
       </c>
       <c r="E23">
-        <v>-25.5526321638808</v>
+        <v>-27.76804768943929</v>
       </c>
       <c r="F23">
-        <v>-1.51197029390068</v>
+        <v>-1.881046905115791</v>
       </c>
       <c r="G23">
-        <v>0.3345791342581086</v>
+        <v>-3.768239542380381</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>8.951075244465434</v>
       </c>
       <c r="E24">
-        <v>-25.44543865564524</v>
+        <v>-28.53099593330358</v>
       </c>
       <c r="F24">
-        <v>-1.273996078057035</v>
+        <v>-2.291266040125746</v>
       </c>
       <c r="G24">
-        <v>0.7815458191517294</v>
+        <v>-2.975065936626397</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>8.696775434070013</v>
       </c>
       <c r="E25">
-        <v>-26.02598449495457</v>
+        <v>-28.93332820651505</v>
       </c>
       <c r="F25">
-        <v>-1.740221961537667</v>
+        <v>-2.207610044484427</v>
       </c>
       <c r="G25">
-        <v>0.4319555207502313</v>
+        <v>-3.374556087941329</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.410645874101403</v>
       </c>
       <c r="E26">
-        <v>-25.79641803360973</v>
+        <v>-28.53076498112918</v>
       </c>
       <c r="F26">
-        <v>-1.33784912256703</v>
+        <v>-1.72693412002936</v>
       </c>
       <c r="G26">
-        <v>0.4279530711932524</v>
+        <v>-3.688683822526154</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.104244838876323</v>
       </c>
       <c r="E27">
-        <v>-26.48280789590034</v>
+        <v>-28.28331557592805</v>
       </c>
       <c r="F27">
-        <v>-1.427333511254446</v>
+        <v>-1.975052523087688</v>
       </c>
       <c r="G27">
-        <v>-0.2514701898313733</v>
+        <v>-3.919981707718414</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.792480788975888</v>
       </c>
       <c r="E28">
-        <v>-25.69429641626276</v>
+        <v>-28.80894461094637</v>
       </c>
       <c r="F28">
-        <v>-1.66485461012876</v>
+        <v>-2.243968746528103</v>
       </c>
       <c r="G28">
-        <v>0.5030759705703942</v>
+        <v>-4.385838365459117</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.492352490616166</v>
       </c>
       <c r="E29">
-        <v>-26.12907520573919</v>
+        <v>-28.04965990255429</v>
       </c>
       <c r="F29">
-        <v>-1.528027367636546</v>
+        <v>-1.578645586152012</v>
       </c>
       <c r="G29">
-        <v>-0.7306253090033278</v>
+        <v>-3.825617917667028</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>7.206009362355526</v>
       </c>
       <c r="E30">
-        <v>-25.6567146104731</v>
+        <v>-28.53260807005031</v>
       </c>
       <c r="F30">
-        <v>-1.439738313111369</v>
+        <v>-2.295764075122947</v>
       </c>
       <c r="G30">
-        <v>0.1003083791715831</v>
+        <v>-3.807224526650838</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.94284514440093</v>
       </c>
       <c r="E31">
-        <v>-25.55853729398681</v>
+        <v>-28.08239624115573</v>
       </c>
       <c r="F31">
-        <v>-1.573556096829212</v>
+        <v>-1.770753927270051</v>
       </c>
       <c r="G31">
-        <v>-1.198852317350148</v>
+        <v>-4.316485746956925</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.710715731280672</v>
       </c>
       <c r="E32">
-        <v>-25.15692051966855</v>
+        <v>-27.16264505630186</v>
       </c>
       <c r="F32">
-        <v>-1.690447021038251</v>
+        <v>-2.181445231699601</v>
       </c>
       <c r="G32">
-        <v>-1.463738997583854</v>
+        <v>-4.499393388001658</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.504031699717926</v>
       </c>
       <c r="E33">
-        <v>-24.23078871493786</v>
+        <v>-27.71329843868656</v>
       </c>
       <c r="F33">
-        <v>-1.847531159998524</v>
+        <v>-2.189405014073102</v>
       </c>
       <c r="G33">
-        <v>-0.9437019515474392</v>
+        <v>-4.117022067670296</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.329388463967012</v>
       </c>
       <c r="E34">
-        <v>-24.80435164732736</v>
+        <v>-27.39323495277243</v>
       </c>
       <c r="F34">
-        <v>-1.732746774094804</v>
+        <v>-2.669843197083565</v>
       </c>
       <c r="G34">
-        <v>-1.5833556290088</v>
+        <v>-5.052724590526522</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.188453303578328</v>
       </c>
       <c r="E35">
-        <v>-24.09192758796666</v>
+        <v>-25.84395795374225</v>
       </c>
       <c r="F35">
-        <v>-1.862052440569599</v>
+        <v>-1.965648067963705</v>
       </c>
       <c r="G35">
-        <v>-1.137507908507453</v>
+        <v>-4.365769838400055</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.071541611187723</v>
       </c>
       <c r="E36">
-        <v>-24.19773538315587</v>
+        <v>-26.03669433598271</v>
       </c>
       <c r="F36">
-        <v>-1.487675934711376</v>
+        <v>-2.053985996165647</v>
       </c>
       <c r="G36">
-        <v>-2.069191429079004</v>
+        <v>-5.186030327756355</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.983780893145552</v>
       </c>
       <c r="E37">
-        <v>-22.53420951338618</v>
+        <v>-26.0556369427568</v>
       </c>
       <c r="F37">
-        <v>-1.41762918713065</v>
+        <v>-2.123550633917944</v>
       </c>
       <c r="G37">
-        <v>-1.913999675289049</v>
+        <v>-5.559562491497863</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.923705904441761</v>
       </c>
       <c r="E38">
-        <v>-21.92559619217731</v>
+        <v>-25.13545555287219</v>
       </c>
       <c r="F38">
-        <v>-1.639720286393017</v>
+        <v>-2.198237895689153</v>
       </c>
       <c r="G38">
-        <v>-2.390711611853022</v>
+        <v>-5.323113397446496</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.880100160114232</v>
       </c>
       <c r="E39">
-        <v>-21.46551681842002</v>
+        <v>-24.46410928123506</v>
       </c>
       <c r="F39">
-        <v>-1.7973991931485</v>
+        <v>-2.024903673388162</v>
       </c>
       <c r="G39">
-        <v>-2.075862178340635</v>
+        <v>-5.470942497957112</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.857568916127061</v>
       </c>
       <c r="E40">
-        <v>-20.98176258255064</v>
+        <v>-23.38127416194295</v>
       </c>
       <c r="F40">
-        <v>-1.368737286282618</v>
+        <v>-1.912256475383666</v>
       </c>
       <c r="G40">
-        <v>-1.873952005900486</v>
+        <v>-5.723937698613756</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.85107992125887</v>
       </c>
       <c r="E41">
-        <v>-20.99480458769273</v>
+        <v>-23.32156623215181</v>
       </c>
       <c r="F41">
-        <v>-1.063203081801451</v>
+        <v>-1.758495746443424</v>
       </c>
       <c r="G41">
-        <v>-2.256568306601753</v>
+        <v>-4.49788377923575</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.848486036957103</v>
       </c>
       <c r="E42">
-        <v>-19.07959518952473</v>
+        <v>-23.42796272896203</v>
       </c>
       <c r="F42">
-        <v>-1.405699039795532</v>
+        <v>-1.9469460171107</v>
       </c>
       <c r="G42">
-        <v>-2.232546988168802</v>
+        <v>-4.852969583232438</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.85028496911413</v>
       </c>
       <c r="E43">
-        <v>-18.86950116641288</v>
+        <v>-22.77683609376914</v>
       </c>
       <c r="F43">
-        <v>-1.421678246995534</v>
+        <v>-1.606949243570866</v>
       </c>
       <c r="G43">
-        <v>-2.358897269220626</v>
+        <v>-4.809687510852007</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.846437628396084</v>
       </c>
       <c r="E44">
-        <v>-18.34743151196459</v>
+        <v>-21.15584165187949</v>
       </c>
       <c r="F44">
-        <v>-1.368666046685977</v>
+        <v>-1.880376755886927</v>
       </c>
       <c r="G44">
-        <v>-2.520216842803771</v>
+        <v>-5.325394363323054</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.82459669093657</v>
       </c>
       <c r="E45">
-        <v>-17.11353555672461</v>
+        <v>-20.18228766734048</v>
       </c>
       <c r="F45">
-        <v>-1.43739817519846</v>
+        <v>-1.79778686909301</v>
       </c>
       <c r="G45">
-        <v>-2.259733188137296</v>
+        <v>-4.930373448486137</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.782800178733461</v>
       </c>
       <c r="E46">
-        <v>-16.55625701686669</v>
+        <v>-20.89570346250887</v>
       </c>
       <c r="F46">
-        <v>-0.967708059239321</v>
+        <v>-1.594995901948469</v>
       </c>
       <c r="G46">
-        <v>-2.905531238119545</v>
+        <v>-5.010485339990962</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.711197304849102</v>
       </c>
       <c r="E47">
-        <v>-15.58777039474226</v>
+        <v>-19.45706161196009</v>
       </c>
       <c r="F47">
-        <v>-1.153030414593626</v>
+        <v>-1.047746574432615</v>
       </c>
       <c r="G47">
-        <v>-2.19780281273415</v>
+        <v>-5.570662750691039</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.601897638681401</v>
       </c>
       <c r="E48">
-        <v>-15.00049524305753</v>
+        <v>-19.45875526123896</v>
       </c>
       <c r="F48">
-        <v>-1.347159143807093</v>
+        <v>-1.196211550566759</v>
       </c>
       <c r="G48">
-        <v>-1.536845774727579</v>
+        <v>-4.576270876514613</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.45469002770441</v>
       </c>
       <c r="E49">
-        <v>-14.22392082090416</v>
+        <v>-18.4481583593172</v>
       </c>
       <c r="F49">
-        <v>-1.292187854589915</v>
+        <v>-1.182826790072325</v>
       </c>
       <c r="G49">
-        <v>-2.042713685855913</v>
+        <v>-5.378647798867771</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.26384579503802</v>
       </c>
       <c r="E50">
-        <v>-13.99082214983334</v>
+        <v>-17.56651881171188</v>
       </c>
       <c r="F50">
-        <v>-1.065559787062415</v>
+        <v>-1.334867828284354</v>
       </c>
       <c r="G50">
-        <v>-2.652198361817895</v>
+        <v>-5.757314618740688</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.029546575136398</v>
       </c>
       <c r="E51">
-        <v>-13.40452062006026</v>
+        <v>-16.88380154184149</v>
       </c>
       <c r="F51">
-        <v>-1.39989301266931</v>
+        <v>-1.357741537377857</v>
       </c>
       <c r="G51">
-        <v>-2.322593826836978</v>
+        <v>-5.646868198459522</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.757175246930678</v>
       </c>
       <c r="E52">
-        <v>-12.76484649563277</v>
+        <v>-15.94049323519971</v>
       </c>
       <c r="F52">
-        <v>-0.9741361902850452</v>
+        <v>-1.515871076000463</v>
       </c>
       <c r="G52">
-        <v>-2.241965490228028</v>
+        <v>-7.002023462232486</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.448253735188212</v>
       </c>
       <c r="E53">
-        <v>-11.47083957641498</v>
+        <v>-14.99690416316945</v>
       </c>
       <c r="F53">
-        <v>-1.269811165938092</v>
+        <v>-0.7859509971866647</v>
       </c>
       <c r="G53">
-        <v>-2.971510410717219</v>
+        <v>-7.036088975831587</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.112398246134143</v>
       </c>
       <c r="E54">
-        <v>-11.45350457791362</v>
+        <v>-15.62030295201336</v>
       </c>
       <c r="F54">
-        <v>-1.361375585173938</v>
+        <v>-1.054530903461543</v>
       </c>
       <c r="G54">
-        <v>-3.395727026664968</v>
+        <v>-5.884750758729393</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.761112882619843</v>
       </c>
       <c r="E55">
-        <v>-11.02667778879465</v>
+        <v>-15.1279446155294</v>
       </c>
       <c r="F55">
-        <v>-0.8175093101311175</v>
+        <v>-1.398616498501596</v>
       </c>
       <c r="G55">
-        <v>-2.764170943592665</v>
+        <v>-6.13332307054557</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.401697554566736</v>
       </c>
       <c r="E56">
-        <v>-10.23448918826284</v>
+        <v>-14.49422543442201</v>
       </c>
       <c r="F56">
-        <v>-1.131685043358289</v>
+        <v>-1.000940502704831</v>
       </c>
       <c r="G56">
-        <v>-3.478371485507334</v>
+        <v>-6.64461034472169</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.048478696566606</v>
       </c>
       <c r="E57">
-        <v>-9.338077758444493</v>
+        <v>-14.5448764161978</v>
       </c>
       <c r="F57">
-        <v>-0.8240666664916784</v>
+        <v>-1.043907919888042</v>
       </c>
       <c r="G57">
-        <v>-3.646689552360499</v>
+        <v>-6.485214198096862</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.712060698986123</v>
       </c>
       <c r="E58">
-        <v>-8.865794147236535</v>
+        <v>-13.66117641291898</v>
       </c>
       <c r="F58">
-        <v>-1.28862670312528</v>
+        <v>-1.520507448353932</v>
       </c>
       <c r="G58">
-        <v>-4.003099574572897</v>
+        <v>-7.700445944106989</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.396511372956629</v>
       </c>
       <c r="E59">
-        <v>-9.76530305327613</v>
+        <v>-13.44190317299358</v>
       </c>
       <c r="F59">
-        <v>-1.499881100024224</v>
+        <v>-1.599094663857521</v>
       </c>
       <c r="G59">
-        <v>-4.472220430215319</v>
+        <v>-7.945661362746345</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.110737314608857</v>
       </c>
       <c r="E60">
-        <v>-8.270082448475515</v>
+        <v>-12.46557323388786</v>
       </c>
       <c r="F60">
-        <v>-1.229125900949595</v>
+        <v>-1.146402647003828</v>
       </c>
       <c r="G60">
-        <v>-4.403076376082102</v>
+        <v>-7.159393554987282</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.856290262667487</v>
       </c>
       <c r="E61">
-        <v>-8.209378254402694</v>
+        <v>-10.62257488224618</v>
       </c>
       <c r="F61">
-        <v>-1.484361636732775</v>
+        <v>-1.679573870509104</v>
       </c>
       <c r="G61">
-        <v>-4.731393108848243</v>
+        <v>-7.712046095676595</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.628344109142414</v>
       </c>
       <c r="E62">
-        <v>-9.1508706429674</v>
+        <v>-11.82851203896281</v>
       </c>
       <c r="F62">
-        <v>-1.32129088655247</v>
+        <v>-1.610645418922157</v>
       </c>
       <c r="G62">
-        <v>-5.084883229895003</v>
+        <v>-7.519726573663714</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.42744763766679</v>
       </c>
       <c r="E63">
-        <v>-8.642313954958004</v>
+        <v>-10.81508936926026</v>
       </c>
       <c r="F63">
-        <v>-1.517896434300308</v>
+        <v>-1.601912769761845</v>
       </c>
       <c r="G63">
-        <v>-4.703303129947527</v>
+        <v>-6.817278468413458</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.247630164035876</v>
       </c>
       <c r="E64">
-        <v>-7.349185559697695</v>
+        <v>-11.31409550558748</v>
       </c>
       <c r="F64">
-        <v>-1.875325371464655</v>
+        <v>-1.599877471053166</v>
       </c>
       <c r="G64">
-        <v>-5.124255547993555</v>
+        <v>-7.587827805952062</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.081537838025104</v>
       </c>
       <c r="E65">
-        <v>-7.085474404335019</v>
+        <v>-11.29547442046794</v>
       </c>
       <c r="F65">
-        <v>-1.782836494207285</v>
+        <v>-1.733989325199004</v>
       </c>
       <c r="G65">
-        <v>-5.18006141414905</v>
+        <v>-8.022449466529741</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.9281297138535375</v>
       </c>
       <c r="E66">
-        <v>-6.67926575737298</v>
+        <v>-10.73428327906739</v>
       </c>
       <c r="F66">
-        <v>-2.025965640398551</v>
+        <v>-2.101655226727147</v>
       </c>
       <c r="G66">
-        <v>-5.365912130178194</v>
+        <v>-8.347879403585639</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.7834805349258696</v>
       </c>
       <c r="E67">
-        <v>-7.015926100525218</v>
+        <v>-11.04874957110804</v>
       </c>
       <c r="F67">
-        <v>-2.207790628578237</v>
+        <v>-2.277158114888667</v>
       </c>
       <c r="G67">
-        <v>-4.986490505922323</v>
+        <v>-7.739934131299417</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.6459529012250171</v>
       </c>
       <c r="E68">
-        <v>-6.444201728582827</v>
+        <v>-10.68462856157329</v>
       </c>
       <c r="F68">
-        <v>-2.215236823162002</v>
+        <v>-1.844137338749254</v>
       </c>
       <c r="G68">
-        <v>-5.599778998708929</v>
+        <v>-8.545929479926997</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.5195785007236127</v>
       </c>
       <c r="E69">
-        <v>-6.556276931798661</v>
+        <v>-11.11692574729352</v>
       </c>
       <c r="F69">
-        <v>-2.247118199393546</v>
+        <v>-2.194453913393165</v>
       </c>
       <c r="G69">
-        <v>-5.699340345256971</v>
+        <v>-8.653333508857573</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.4074360668843409</v>
       </c>
       <c r="E70">
-        <v>-6.42724712189811</v>
+        <v>-10.43135553879829</v>
       </c>
       <c r="F70">
-        <v>-2.267598755060361</v>
+        <v>-2.141052380404292</v>
       </c>
       <c r="G70">
-        <v>-5.626286536841874</v>
+        <v>-8.083022518261785</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.3138206313973921</v>
       </c>
       <c r="E71">
-        <v>-6.327113504640502</v>
+        <v>-10.94991109741663</v>
       </c>
       <c r="F71">
-        <v>-2.197581000338733</v>
+        <v>-2.389938680045014</v>
       </c>
       <c r="G71">
-        <v>-5.330661441276035</v>
+        <v>-7.540659153108527</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.2455820109188346</v>
       </c>
       <c r="E72">
-        <v>-5.837644334573437</v>
+        <v>-10.66742941729216</v>
       </c>
       <c r="F72">
-        <v>-2.36760589486554</v>
+        <v>-2.386180377138513</v>
       </c>
       <c r="G72">
-        <v>-5.239025540749008</v>
+        <v>-7.490348792548222</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.2065976860389512</v>
       </c>
       <c r="E73">
-        <v>-7.507546295745927</v>
+        <v>-10.23665832731251</v>
       </c>
       <c r="F73">
-        <v>-2.548773987694806</v>
+        <v>-2.37280472868551</v>
       </c>
       <c r="G73">
-        <v>-4.901005599007263</v>
+        <v>-7.937911375638912</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.19983920721115</v>
       </c>
       <c r="E74">
-        <v>-6.758717833837557</v>
+        <v>-11.30385662585614</v>
       </c>
       <c r="F74">
-        <v>-2.851054365017776</v>
+        <v>-2.480592723505184</v>
       </c>
       <c r="G74">
-        <v>-4.580342847527917</v>
+        <v>-8.217371077336489</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.2289721383884018</v>
       </c>
       <c r="E75">
-        <v>-6.08627567149057</v>
+        <v>-11.03427203970552</v>
       </c>
       <c r="F75">
-        <v>-2.704434991457069</v>
+        <v>-2.513338915305251</v>
       </c>
       <c r="G75">
-        <v>-4.242187173419062</v>
+        <v>-7.571722001903508</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.2939076234150453</v>
       </c>
       <c r="E76">
-        <v>-7.580463784217435</v>
+        <v>-11.66613907494378</v>
       </c>
       <c r="F76">
-        <v>-2.810848724755499</v>
+        <v>-2.707995314554302</v>
       </c>
       <c r="G76">
-        <v>-3.548862931675036</v>
+        <v>-6.583027576600168</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3926400281143623</v>
       </c>
       <c r="E77">
-        <v>-8.004736513996072</v>
+        <v>-12.46604419518466</v>
       </c>
       <c r="F77">
-        <v>-2.901183846765591</v>
+        <v>-2.583584471062649</v>
       </c>
       <c r="G77">
-        <v>-3.845851972003054</v>
+        <v>-6.649764864126336</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.5224883382878464</v>
       </c>
       <c r="E78">
-        <v>-8.389222071143315</v>
+        <v>-11.80525832493342</v>
       </c>
       <c r="F78">
-        <v>-2.528751519201739</v>
+        <v>-2.971023502495617</v>
       </c>
       <c r="G78">
-        <v>-3.664980316464973</v>
+        <v>-7.836274317037747</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.6765887776984997</v>
       </c>
       <c r="E79">
-        <v>-8.453390547832004</v>
+        <v>-11.84456547932</v>
       </c>
       <c r="F79">
-        <v>-2.906318896295545</v>
+        <v>-2.685530818957782</v>
       </c>
       <c r="G79">
-        <v>-3.075190075916114</v>
+        <v>-7.08027482714424</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.8465003395049381</v>
       </c>
       <c r="E80">
-        <v>-9.803890180295488</v>
+        <v>-13.16386845434464</v>
       </c>
       <c r="F80">
-        <v>-3.139306340374337</v>
+        <v>-2.886535825981888</v>
       </c>
       <c r="G80">
-        <v>-3.046312187177052</v>
+        <v>-5.922179786596393</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.023850213121348</v>
       </c>
       <c r="E81">
-        <v>-10.60801130983751</v>
+        <v>-13.50522935351684</v>
       </c>
       <c r="F81">
-        <v>-3.287415118525277</v>
+        <v>-2.991011179557767</v>
       </c>
       <c r="G81">
-        <v>-3.429819024628384</v>
+        <v>-6.570848079561189</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.198313966997302</v>
       </c>
       <c r="E82">
-        <v>-12.03997818969899</v>
+        <v>-14.52635495750643</v>
       </c>
       <c r="F82">
-        <v>-3.099055968272309</v>
+        <v>-2.938797525424508</v>
       </c>
       <c r="G82">
-        <v>-2.924907861160899</v>
+        <v>-5.409343177107893</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.36035097153682</v>
       </c>
       <c r="E83">
-        <v>-11.57102300688667</v>
+        <v>-14.74993024773912</v>
       </c>
       <c r="F83">
-        <v>-2.972715028732134</v>
+        <v>-2.912831520816355</v>
       </c>
       <c r="G83">
-        <v>-2.271200917885332</v>
+        <v>-5.941801390007653</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.501614876710848</v>
       </c>
       <c r="E84">
-        <v>-12.78910100241786</v>
+        <v>-16.32797211366602</v>
       </c>
       <c r="F84">
-        <v>-2.954068478495117</v>
+        <v>-3.219178353719668</v>
       </c>
       <c r="G84">
-        <v>-2.360228108527413</v>
+        <v>-5.034579490425777</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.613651301211168</v>
       </c>
       <c r="E85">
-        <v>-13.24996833065248</v>
+        <v>-16.86707335885715</v>
       </c>
       <c r="F85">
-        <v>-2.922299760230353</v>
+        <v>-3.415207357755157</v>
       </c>
       <c r="G85">
-        <v>-1.691845516876256</v>
+        <v>-4.882834014542204</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.690242584281546</v>
       </c>
       <c r="E86">
-        <v>-15.05989070814213</v>
+        <v>-18.57523639692045</v>
       </c>
       <c r="F86">
-        <v>-3.186322817422431</v>
+        <v>-3.205052204399728</v>
       </c>
       <c r="G86">
-        <v>-1.903720431389612</v>
+        <v>-4.692828563861273</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.726723861676002</v>
       </c>
       <c r="E87">
-        <v>-15.74336876164582</v>
+        <v>-19.62809301828178</v>
       </c>
       <c r="F87">
-        <v>-3.325732081109171</v>
+        <v>-3.117627137075671</v>
       </c>
       <c r="G87">
-        <v>-0.7884075708457671</v>
+        <v>-4.390939916135133</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.719482692436599</v>
       </c>
       <c r="E88">
-        <v>-17.10139018943604</v>
+        <v>-20.02915731877111</v>
       </c>
       <c r="F88">
-        <v>-3.067440497977063</v>
+        <v>-3.346624335375178</v>
       </c>
       <c r="G88">
-        <v>-1.291726361908862</v>
+        <v>-5.214027611381971</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.667482364343953</v>
       </c>
       <c r="E89">
-        <v>-18.9228873464893</v>
+        <v>-21.58640443205478</v>
       </c>
       <c r="F89">
-        <v>-3.244390543991274</v>
+        <v>-3.61849865881099</v>
       </c>
       <c r="G89">
-        <v>-1.840459216679679</v>
+        <v>-3.834397484437176</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.57098520341606</v>
       </c>
       <c r="E90">
-        <v>-20.70365540831758</v>
+        <v>-22.82042265609297</v>
       </c>
       <c r="F90">
-        <v>-3.149698209442457</v>
+        <v>-3.339555876327089</v>
       </c>
       <c r="G90">
-        <v>-1.385570396310582</v>
+        <v>-4.842293073868289</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.432311554652298</v>
       </c>
       <c r="E91">
-        <v>-22.73542772744301</v>
+        <v>-23.5303198269574</v>
       </c>
       <c r="F91">
-        <v>-3.29827832864559</v>
+        <v>-3.607121032533538</v>
       </c>
       <c r="G91">
-        <v>-1.1545572180347</v>
+        <v>-5.301270417978385</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.25585391999351</v>
       </c>
       <c r="E92">
-        <v>-23.91698358010233</v>
+        <v>-26.26482527106712</v>
       </c>
       <c r="F92">
-        <v>-2.991237323858731</v>
+        <v>-3.643492160088256</v>
       </c>
       <c r="G92">
-        <v>-1.806982980186569</v>
+        <v>-4.733975334368875</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.046623578123008</v>
       </c>
       <c r="E93">
-        <v>-26.26697629622076</v>
+        <v>-27.4949399505107</v>
       </c>
       <c r="F93">
-        <v>-3.500234301448109</v>
+        <v>-4.026791011242032</v>
       </c>
       <c r="G93">
-        <v>-1.627081314491494</v>
+        <v>-4.774344126674747</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.8122528646562572</v>
       </c>
       <c r="E94">
-        <v>-28.01060181423813</v>
+        <v>-29.70100417724334</v>
       </c>
       <c r="F94">
-        <v>-3.667283700264061</v>
+        <v>-4.056338876499891</v>
       </c>
       <c r="G94">
-        <v>-2.025634581418813</v>
+        <v>-4.349313116524337</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.5618221778821257</v>
       </c>
       <c r="E95">
-        <v>-30.27193380199739</v>
+        <v>-31.43096502494256</v>
       </c>
       <c r="F95">
-        <v>-3.316035212292</v>
+        <v>-4.006341933536524</v>
       </c>
       <c r="G95">
-        <v>-2.19212853767984</v>
+        <v>-5.029775888848294</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3045962634850515</v>
       </c>
       <c r="E96">
-        <v>-32.38073772823029</v>
+        <v>-33.73126453153782</v>
       </c>
       <c r="F96">
-        <v>-4.051241103503062</v>
+        <v>-4.398129893834189</v>
       </c>
       <c r="G96">
-        <v>-2.254677985098829</v>
+        <v>-5.24051528624168</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.05192315524792241</v>
       </c>
       <c r="E97">
-        <v>-34.13803923775082</v>
+        <v>-36.00330862456223</v>
       </c>
       <c r="F97">
-        <v>-3.917053039556168</v>
+        <v>-4.654832668287727</v>
       </c>
       <c r="G97">
-        <v>-2.787238824910307</v>
+        <v>-5.595031676405614</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.1851700306981777</v>
       </c>
       <c r="E98">
-        <v>-36.91713882965108</v>
+        <v>-37.37527548805907</v>
       </c>
       <c r="F98">
-        <v>-3.686829029133115</v>
+        <v>-4.851680927684585</v>
       </c>
       <c r="G98">
-        <v>-2.746906448605366</v>
+        <v>-6.697344024616741</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.3986526584416494</v>
       </c>
       <c r="E99">
-        <v>-39.84825702975182</v>
+        <v>-40.34683975375933</v>
       </c>
       <c r="F99">
-        <v>-4.014765601655592</v>
+        <v>-5.036996656099668</v>
       </c>
       <c r="G99">
-        <v>-3.201560220241174</v>
+        <v>-6.403655598191376</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.5787817302206578</v>
       </c>
       <c r="E100">
-        <v>-40.34941192699569</v>
+        <v>-42.25906941603027</v>
       </c>
       <c r="F100">
-        <v>-3.991904318073131</v>
+        <v>-5.565111524978257</v>
       </c>
       <c r="G100">
-        <v>-3.01865588974198</v>
+        <v>-7.271770023317842</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.7206374882107572</v>
       </c>
       <c r="E101">
-        <v>-42.34898226745257</v>
+        <v>-44.56855040367608</v>
       </c>
       <c r="F101">
-        <v>-4.212164725375311</v>
+        <v>-5.458177576950868</v>
       </c>
       <c r="G101">
-        <v>-3.783395219859164</v>
+        <v>-6.972658923299151</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.8180734336329067</v>
       </c>
       <c r="E102">
-        <v>-45.53023299360399</v>
+        <v>-46.50049477753942</v>
       </c>
       <c r="F102">
-        <v>-4.339236284964755</v>
+        <v>-6.00501769096974</v>
       </c>
       <c r="G102">
-        <v>-5.21807971912204</v>
+        <v>-7.420787609677056</v>
       </c>
     </row>
   </sheetData>
